--- a/04_Figures/shared/WGCNA/preservation/c_data/preservation.xlsx
+++ b/04_Figures/shared/WGCNA/preservation/c_data/preservation.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="preservation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="arm_sizes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="arm_native" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="arm_sizes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">reference</t>
   </si>
@@ -70,6 +71,33 @@
   </si>
   <si>
     <t xml:space="preserve">yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_ref_modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grey60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightcyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightgreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightyellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">midnightblue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tan</t>
   </si>
   <si>
     <t xml:space="preserve">group</t>
@@ -880,13 +908,806 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.26327115653097</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>165</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.56390748879768</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>133</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.4403708700652</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
+      <c r="D5" t="n">
+        <v>57</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.88696353727924</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.3419521731192</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.87341968751282</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.42501958263082</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="n">
+        <v>46</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.58166563351445</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.18386520484002</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.87453058100512</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="n">
+        <v>96</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.0872535741041</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>53</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.20546090516745</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="n">
+        <v>102</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.55649810162138</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>71</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15.0857718797711</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>122</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.01308522393866</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.63840293609037</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="n">
+        <v>61</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.1831894503239</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="n">
+        <v>207</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12.4067780887991</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>130</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.01214845293346</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>105</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.8112246488008</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>186</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.83376784198413</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>149</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4.79294778572968</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>47</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.1388010086203</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="n">
+        <v>123</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.5335357173769</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="n">
+        <v>79</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.23157253339458</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="n">
+        <v>91</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.68520616463463</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.48556341458288</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>88</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.2605648534057</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="n">
+        <v>115</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.4362445588423</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" t="n">
+        <v>53</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.41187528581256</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>57</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.59415371548382</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="n">
+        <v>349</v>
+      </c>
+      <c r="E33" t="n">
+        <v>31.734045211765</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="n">
+        <v>126</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.40320248159551</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
